--- a/samples/ozon_analitika_wide.xlsx
+++ b/samples/ozon_analitika_wide.xlsx
@@ -410,214 +410,214 @@
         <v>Показатель</v>
       </c>
       <c r="B2" t="str">
-        <v>15.07.2026</v>
+        <v>20.07.2026</v>
       </c>
       <c r="C2" t="str">
-        <v>16.07.2026</v>
+        <v>21.07.2026</v>
       </c>
       <c r="D2" t="str">
-        <v>17.07.2026</v>
+        <v>22.07.2026</v>
       </c>
       <c r="E2" t="str">
-        <v>18.07.2026</v>
+        <v>23.07.2026</v>
       </c>
       <c r="F2" t="str">
-        <v>19.07.2026</v>
+        <v>24.07.2026</v>
       </c>
       <c r="G2" t="str">
-        <v>20.07.2026</v>
+        <v>25.07.2026</v>
       </c>
       <c r="H2" t="str">
-        <v>21.07.2026</v>
+        <v>26.07.2026</v>
       </c>
       <c r="I2" t="str">
-        <v>22.07.2026</v>
+        <v>27.07.2026</v>
       </c>
       <c r="J2" t="str">
-        <v>23.07.2026</v>
+        <v>28.07.2026</v>
       </c>
       <c r="K2" t="str">
-        <v>24.07.2026</v>
+        <v>29.07.2026</v>
       </c>
       <c r="L2" t="str">
-        <v>25.07.2026</v>
+        <v>30.07.2026</v>
       </c>
       <c r="M2" t="str">
-        <v>26.07.2026</v>
+        <v>31.07.2026</v>
       </c>
       <c r="N2" t="str">
-        <v>27.07.2026</v>
+        <v>01.08.2026</v>
       </c>
       <c r="O2" t="str">
-        <v>28.07.2026</v>
+        <v>02.08.2026</v>
       </c>
       <c r="P2" t="str">
-        <v>29.07.2026</v>
+        <v>03.08.2026</v>
       </c>
       <c r="Q2" t="str">
-        <v>30.07.2026</v>
+        <v>04.08.2026</v>
       </c>
       <c r="R2" t="str">
-        <v>31.07.2026</v>
+        <v>05.08.2026</v>
       </c>
       <c r="S2" t="str">
-        <v>01.08.2026</v>
+        <v>06.08.2026</v>
       </c>
       <c r="T2" t="str">
-        <v>02.08.2026</v>
+        <v>07.08.2026</v>
       </c>
       <c r="U2" t="str">
-        <v>03.08.2026</v>
+        <v>08.08.2026</v>
       </c>
       <c r="V2" t="str">
-        <v>04.08.2026</v>
+        <v>09.08.2026</v>
       </c>
       <c r="W2" t="str">
-        <v>05.08.2026</v>
+        <v>10.08.2026</v>
       </c>
       <c r="X2" t="str">
-        <v>06.08.2026</v>
+        <v>11.08.2026</v>
       </c>
       <c r="Y2" t="str">
-        <v>07.08.2026</v>
+        <v>12.08.2026</v>
       </c>
       <c r="Z2" t="str">
-        <v>08.08.2026</v>
+        <v>13.08.2026</v>
       </c>
       <c r="AA2" t="str">
-        <v>09.08.2026</v>
+        <v>14.08.2026</v>
       </c>
       <c r="AB2" t="str">
-        <v>10.08.2026</v>
+        <v>15.08.2026</v>
       </c>
       <c r="AC2" t="str">
-        <v>11.08.2026</v>
+        <v>16.08.2026</v>
       </c>
       <c r="AD2" t="str">
-        <v>12.08.2026</v>
+        <v>17.08.2026</v>
       </c>
       <c r="AE2" t="str">
-        <v>13.08.2026</v>
+        <v>18.08.2026</v>
       </c>
       <c r="AF2" t="str">
-        <v>14.08.2026</v>
+        <v>19.08.2026</v>
       </c>
       <c r="AG2" t="str">
-        <v>15.08.2026</v>
+        <v>20.08.2026</v>
       </c>
       <c r="AH2" t="str">
-        <v>16.08.2026</v>
+        <v>21.08.2026</v>
       </c>
       <c r="AI2" t="str">
-        <v>17.08.2026</v>
+        <v>22.08.2026</v>
       </c>
       <c r="AJ2" t="str">
-        <v>18.08.2026</v>
+        <v>23.08.2026</v>
       </c>
       <c r="AK2" t="str">
-        <v>19.08.2026</v>
+        <v>24.08.2026</v>
       </c>
       <c r="AL2" t="str">
-        <v>20.08.2026</v>
+        <v>25.08.2026</v>
       </c>
       <c r="AM2" t="str">
-        <v>21.08.2026</v>
+        <v>26.08.2026</v>
       </c>
       <c r="AN2" t="str">
-        <v>22.08.2026</v>
+        <v>27.08.2026</v>
       </c>
       <c r="AO2" t="str">
-        <v>23.08.2026</v>
+        <v>28.08.2026</v>
       </c>
       <c r="AP2" t="str">
-        <v>24.08.2026</v>
+        <v>29.08.2026</v>
       </c>
       <c r="AQ2" t="str">
-        <v>25.08.2026</v>
+        <v>30.08.2026</v>
       </c>
       <c r="AR2" t="str">
-        <v>26.08.2026</v>
+        <v>31.08.2026</v>
       </c>
       <c r="AS2" t="str">
-        <v>27.08.2026</v>
+        <v>01.09.2026</v>
       </c>
       <c r="AT2" t="str">
-        <v>28.08.2026</v>
+        <v>02.09.2026</v>
       </c>
       <c r="AU2" t="str">
-        <v>29.08.2026</v>
+        <v>03.09.2026</v>
       </c>
       <c r="AV2" t="str">
-        <v>30.08.2026</v>
+        <v>04.09.2026</v>
       </c>
       <c r="AW2" t="str">
-        <v>31.08.2026</v>
+        <v>05.09.2026</v>
       </c>
       <c r="AX2" t="str">
-        <v>01.09.2026</v>
+        <v>06.09.2026</v>
       </c>
       <c r="AY2" t="str">
-        <v>02.09.2026</v>
+        <v>07.09.2026</v>
       </c>
       <c r="AZ2" t="str">
-        <v>03.09.2026</v>
+        <v>08.09.2026</v>
       </c>
       <c r="BA2" t="str">
-        <v>04.09.2026</v>
+        <v>09.09.2026</v>
       </c>
       <c r="BB2" t="str">
-        <v>05.09.2026</v>
+        <v>10.09.2026</v>
       </c>
       <c r="BC2" t="str">
-        <v>06.09.2026</v>
+        <v>11.09.2026</v>
       </c>
       <c r="BD2" t="str">
-        <v>07.09.2026</v>
+        <v>12.09.2026</v>
       </c>
       <c r="BE2" t="str">
-        <v>08.09.2026</v>
+        <v>13.09.2026</v>
       </c>
       <c r="BF2" t="str">
-        <v>09.09.2026</v>
+        <v>14.09.2026</v>
       </c>
       <c r="BG2" t="str">
-        <v>10.09.2026</v>
+        <v>15.09.2026</v>
       </c>
       <c r="BH2" t="str">
-        <v>11.09.2026</v>
+        <v>16.09.2026</v>
       </c>
       <c r="BI2" t="str">
-        <v>12.09.2026</v>
+        <v>17.09.2026</v>
       </c>
       <c r="BJ2" t="str">
-        <v>13.09.2026</v>
+        <v>18.09.2026</v>
       </c>
       <c r="BK2" t="str">
-        <v>14.09.2026</v>
+        <v>19.09.2026</v>
       </c>
       <c r="BL2" t="str">
-        <v>15.09.2026</v>
+        <v>20.09.2026</v>
       </c>
       <c r="BM2" t="str">
-        <v>16.09.2026</v>
+        <v>21.09.2026</v>
       </c>
       <c r="BN2" t="str">
-        <v>17.09.2026</v>
+        <v>22.09.2026</v>
       </c>
       <c r="BO2" t="str">
-        <v>18.09.2026</v>
+        <v>23.09.2026</v>
       </c>
       <c r="BP2" t="str">
-        <v>19.09.2026</v>
+        <v>24.09.2026</v>
       </c>
       <c r="BQ2" t="str">
-        <v>20.09.2026</v>
+        <v>25.09.2026</v>
       </c>
       <c r="BR2" t="str">
-        <v>21.09.2026</v>
+        <v>26.09.2026</v>
       </c>
       <c r="BS2" t="str">
-        <v>22.09.2026</v>
+        <v>27.09.2026</v>
       </c>
     </row>
     <row r="3">
@@ -634,16 +634,16 @@
         <v>10306</v>
       </c>
       <c r="E3">
-        <v>11281</v>
+        <v>10297</v>
       </c>
       <c r="F3">
-        <v>11143</v>
+        <v>10168</v>
       </c>
       <c r="G3">
-        <v>9930</v>
+        <v>10886</v>
       </c>
       <c r="H3">
-        <v>9012</v>
+        <v>9883</v>
       </c>
       <c r="I3">
         <v>10460</v>
@@ -655,16 +655,16 @@
         <v>10121</v>
       </c>
       <c r="L3">
-        <v>10119</v>
+        <v>9217</v>
       </c>
       <c r="M3">
-        <v>11074</v>
+        <v>10085</v>
       </c>
       <c r="N3">
-        <v>9418</v>
+        <v>10344</v>
       </c>
       <c r="O3">
-        <v>9563</v>
+        <v>10505</v>
       </c>
       <c r="P3">
         <v>9417</v>
@@ -676,16 +676,16 @@
         <v>9258</v>
       </c>
       <c r="S3">
-        <v>10121</v>
+        <v>9207</v>
       </c>
       <c r="T3">
-        <v>11092</v>
+        <v>10089</v>
       </c>
       <c r="U3">
-        <v>9153</v>
+        <v>10065</v>
       </c>
       <c r="V3">
-        <v>9888</v>
+        <v>10873</v>
       </c>
       <c r="W3">
         <v>9334</v>
@@ -697,16 +697,16 @@
         <v>10281</v>
       </c>
       <c r="Z3">
-        <v>10157</v>
+        <v>9235</v>
       </c>
       <c r="AA3">
-        <v>11030</v>
+        <v>10029</v>
       </c>
       <c r="AB3">
-        <v>9145</v>
+        <v>10057</v>
       </c>
       <c r="AC3">
-        <v>9154</v>
+        <v>10067</v>
       </c>
       <c r="AD3">
         <v>10204</v>
@@ -718,16 +718,16 @@
         <v>9584</v>
       </c>
       <c r="AG3">
-        <v>11295</v>
+        <v>10275</v>
       </c>
       <c r="AH3">
-        <v>11354</v>
+        <v>10331</v>
       </c>
       <c r="AI3">
-        <v>9078</v>
+        <v>9975</v>
       </c>
       <c r="AJ3">
-        <v>10190</v>
+        <v>11194</v>
       </c>
       <c r="AK3">
         <v>10002</v>
@@ -739,16 +739,16 @@
         <v>9296</v>
       </c>
       <c r="AN3">
-        <v>10728</v>
+        <v>9776</v>
       </c>
       <c r="AO3">
-        <v>10664</v>
+        <v>9720</v>
       </c>
       <c r="AP3">
-        <v>10464</v>
+        <v>11477</v>
       </c>
       <c r="AQ3">
-        <v>9846</v>
+        <v>10795</v>
       </c>
       <c r="AR3">
         <v>10293</v>
@@ -760,16 +760,16 @@
         <v>9958</v>
       </c>
       <c r="AU3">
-        <v>10926</v>
+        <v>9980</v>
       </c>
       <c r="AV3">
-        <v>11831</v>
+        <v>10811</v>
       </c>
       <c r="AW3">
-        <v>10357</v>
+        <v>11329</v>
       </c>
       <c r="AX3">
-        <v>9567</v>
+        <v>10460</v>
       </c>
       <c r="AY3">
         <v>10230</v>
@@ -781,16 +781,16 @@
         <v>10861</v>
       </c>
       <c r="BB3">
-        <v>12196</v>
+        <v>11174</v>
       </c>
       <c r="BC3">
-        <v>11006</v>
+        <v>10089</v>
       </c>
       <c r="BD3">
-        <v>10266</v>
+        <v>11194</v>
       </c>
       <c r="BE3">
-        <v>11469</v>
+        <v>12500</v>
       </c>
       <c r="BF3">
         <v>10182</v>
@@ -802,16 +802,16 @@
         <v>11114</v>
       </c>
       <c r="BI3">
-        <v>11650</v>
+        <v>10709</v>
       </c>
       <c r="BJ3">
-        <v>11833</v>
+        <v>10882</v>
       </c>
       <c r="BK3">
-        <v>11294</v>
+        <v>12275</v>
       </c>
       <c r="BL3">
-        <v>11675</v>
+        <v>12683</v>
       </c>
       <c r="BM3">
         <v>11435</v>
@@ -823,16 +823,16 @@
         <v>10683</v>
       </c>
       <c r="BP3">
-        <v>11596</v>
+        <v>10693</v>
       </c>
       <c r="BQ3">
-        <v>12370</v>
+        <v>11411</v>
       </c>
       <c r="BR3">
-        <v>10377</v>
+        <v>11243</v>
       </c>
       <c r="BS3">
-        <v>11021</v>
+        <v>11936</v>
       </c>
     </row>
     <row r="4">
@@ -849,16 +849,16 @@
         <v>548</v>
       </c>
       <c r="E4">
-        <v>566</v>
+        <v>517</v>
       </c>
       <c r="F4">
-        <v>608</v>
+        <v>555</v>
       </c>
       <c r="G4">
-        <v>509</v>
+        <v>558</v>
       </c>
       <c r="H4">
-        <v>446</v>
+        <v>489</v>
       </c>
       <c r="I4">
         <v>541</v>
@@ -870,16 +870,16 @@
         <v>534</v>
       </c>
       <c r="L4">
-        <v>510</v>
+        <v>464</v>
       </c>
       <c r="M4">
-        <v>562</v>
+        <v>512</v>
       </c>
       <c r="N4">
-        <v>517</v>
+        <v>567</v>
       </c>
       <c r="O4">
-        <v>500</v>
+        <v>549</v>
       </c>
       <c r="P4">
         <v>466</v>
@@ -891,16 +891,16 @@
         <v>462</v>
       </c>
       <c r="S4">
-        <v>524</v>
+        <v>477</v>
       </c>
       <c r="T4">
-        <v>556</v>
+        <v>506</v>
       </c>
       <c r="U4">
-        <v>463</v>
+        <v>510</v>
       </c>
       <c r="V4">
-        <v>537</v>
+        <v>590</v>
       </c>
       <c r="W4">
         <v>477</v>
@@ -912,16 +912,16 @@
         <v>553</v>
       </c>
       <c r="Z4">
-        <v>544</v>
+        <v>495</v>
       </c>
       <c r="AA4">
-        <v>559</v>
+        <v>508</v>
       </c>
       <c r="AB4">
-        <v>482</v>
+        <v>530</v>
       </c>
       <c r="AC4">
-        <v>496</v>
+        <v>546</v>
       </c>
       <c r="AD4">
         <v>519</v>
@@ -933,16 +933,16 @@
         <v>503</v>
       </c>
       <c r="AG4">
-        <v>579</v>
+        <v>527</v>
       </c>
       <c r="AH4">
-        <v>566</v>
+        <v>515</v>
       </c>
       <c r="AI4">
-        <v>455</v>
+        <v>500</v>
       </c>
       <c r="AJ4">
-        <v>525</v>
+        <v>577</v>
       </c>
       <c r="AK4">
         <v>536</v>
@@ -954,16 +954,16 @@
         <v>470</v>
       </c>
       <c r="AN4">
-        <v>569</v>
+        <v>519</v>
       </c>
       <c r="AO4">
+        <v>488</v>
+      </c>
+      <c r="AP4">
+        <v>574</v>
+      </c>
+      <c r="AQ4">
         <v>535</v>
-      </c>
-      <c r="AP4">
-        <v>523</v>
-      </c>
-      <c r="AQ4">
-        <v>488</v>
       </c>
       <c r="AR4">
         <v>566</v>
@@ -975,16 +975,16 @@
         <v>499</v>
       </c>
       <c r="AU4">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="AV4">
-        <v>618</v>
+        <v>565</v>
       </c>
       <c r="AW4">
-        <v>519</v>
+        <v>568</v>
       </c>
       <c r="AX4">
-        <v>504</v>
+        <v>551</v>
       </c>
       <c r="AY4">
         <v>532</v>
@@ -996,16 +996,16 @@
         <v>584</v>
       </c>
       <c r="BB4">
-        <v>637</v>
+        <v>583</v>
       </c>
       <c r="BC4">
+        <v>533</v>
+      </c>
+      <c r="BD4">
         <v>582</v>
       </c>
-      <c r="BD4">
-        <v>534</v>
-      </c>
       <c r="BE4">
-        <v>594</v>
+        <v>648</v>
       </c>
       <c r="BF4">
         <v>500</v>
@@ -1017,16 +1017,16 @@
         <v>585</v>
       </c>
       <c r="BI4">
-        <v>596</v>
+        <v>548</v>
       </c>
       <c r="BJ4">
-        <v>590</v>
+        <v>543</v>
       </c>
       <c r="BK4">
-        <v>570</v>
+        <v>620</v>
       </c>
       <c r="BL4">
-        <v>623</v>
+        <v>676</v>
       </c>
       <c r="BM4">
         <v>583</v>
@@ -1038,16 +1038,16 @@
         <v>573</v>
       </c>
       <c r="BP4">
-        <v>636</v>
+        <v>586</v>
       </c>
       <c r="BQ4">
-        <v>615</v>
+        <v>568</v>
       </c>
       <c r="BR4">
-        <v>514</v>
+        <v>557</v>
       </c>
       <c r="BS4">
-        <v>554</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5">
@@ -1064,16 +1064,16 @@
         <v>60</v>
       </c>
       <c r="E5">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F5">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G5">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I5">
         <v>62</v>
@@ -1085,16 +1085,16 @@
         <v>59</v>
       </c>
       <c r="L5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M5">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N5">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P5">
         <v>49</v>
@@ -1106,16 +1106,16 @@
         <v>51</v>
       </c>
       <c r="S5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="T5">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="U5">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="V5">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="W5">
         <v>45</v>
@@ -1127,16 +1127,16 @@
         <v>54</v>
       </c>
       <c r="Z5">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="AA5">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="AB5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AC5">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AD5">
         <v>49</v>
@@ -1148,16 +1148,16 @@
         <v>51</v>
       </c>
       <c r="AG5">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="AH5">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AI5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AK5">
         <v>61</v>
@@ -1169,16 +1169,16 @@
         <v>51</v>
       </c>
       <c r="AN5">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="AO5">
+        <v>54</v>
+      </c>
+      <c r="AP5">
+        <v>65</v>
+      </c>
+      <c r="AQ5">
         <v>60</v>
-      </c>
-      <c r="AP5">
-        <v>59</v>
-      </c>
-      <c r="AQ5">
-        <v>54</v>
       </c>
       <c r="AR5">
         <v>60</v>
@@ -1190,16 +1190,16 @@
         <v>55</v>
       </c>
       <c r="AU5">
+        <v>60</v>
+      </c>
+      <c r="AV5">
         <v>65</v>
       </c>
-      <c r="AV5">
-        <v>71</v>
-      </c>
       <c r="AW5">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AX5">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AY5">
         <v>59</v>
@@ -1211,16 +1211,16 @@
         <v>66</v>
       </c>
       <c r="BB5">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="BC5">
+        <v>55</v>
+      </c>
+      <c r="BD5">
         <v>60</v>
       </c>
-      <c r="BD5">
-        <v>55</v>
-      </c>
       <c r="BE5">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="BF5">
         <v>51</v>
@@ -1232,16 +1232,16 @@
         <v>61</v>
       </c>
       <c r="BI5">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="BJ5">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="BK5">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="BL5">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="BM5">
         <v>67</v>
@@ -1253,16 +1253,16 @@
         <v>66</v>
       </c>
       <c r="BP5">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="BQ5">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="BR5">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="BS5">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1279,16 +1279,16 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F6">
+        <v>25</v>
+      </c>
+      <c r="G6">
         <v>27</v>
       </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
       <c r="H6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I6">
         <v>25</v>
@@ -1300,16 +1300,16 @@
         <v>25</v>
       </c>
       <c r="L6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P6">
         <v>20</v>
@@ -1321,16 +1321,16 @@
         <v>20</v>
       </c>
       <c r="S6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="T6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W6">
         <v>19</v>
@@ -1342,16 +1342,16 @@
         <v>22</v>
       </c>
       <c r="Z6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AC6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AD6">
         <v>19</v>
@@ -1363,16 +1363,16 @@
         <v>22</v>
       </c>
       <c r="AG6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH6">
+        <v>23</v>
+      </c>
+      <c r="AI6">
+        <v>22</v>
+      </c>
+      <c r="AJ6">
         <v>25</v>
-      </c>
-      <c r="AI6">
-        <v>20</v>
-      </c>
-      <c r="AJ6">
-        <v>23</v>
       </c>
       <c r="AK6">
         <v>24</v>
@@ -1384,16 +1384,16 @@
         <v>21</v>
       </c>
       <c r="AN6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO6">
+        <v>22</v>
+      </c>
+      <c r="AP6">
+        <v>26</v>
+      </c>
+      <c r="AQ6">
         <v>24</v>
-      </c>
-      <c r="AP6">
-        <v>23</v>
-      </c>
-      <c r="AQ6">
-        <v>22</v>
       </c>
       <c r="AR6">
         <v>26</v>
@@ -1405,16 +1405,16 @@
         <v>22</v>
       </c>
       <c r="AU6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AW6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY6">
         <v>26</v>
@@ -1426,16 +1426,16 @@
         <v>25</v>
       </c>
       <c r="BB6">
+        <v>25</v>
+      </c>
+      <c r="BC6">
+        <v>22</v>
+      </c>
+      <c r="BD6">
+        <v>24</v>
+      </c>
+      <c r="BE6">
         <v>28</v>
-      </c>
-      <c r="BC6">
-        <v>24</v>
-      </c>
-      <c r="BD6">
-        <v>22</v>
-      </c>
-      <c r="BE6">
-        <v>26</v>
       </c>
       <c r="BF6">
         <v>21</v>
@@ -1447,16 +1447,16 @@
         <v>24</v>
       </c>
       <c r="BI6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BJ6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BK6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BL6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BM6">
         <v>27</v>
@@ -1468,16 +1468,16 @@
         <v>27</v>
       </c>
       <c r="BP6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BQ6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BR6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BS6">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -1494,16 +1494,16 @@
         <v>29 440 ₽</v>
       </c>
       <c r="E7" t="str">
-        <v>37 120 ₽</v>
+        <v>34 560 ₽</v>
       </c>
       <c r="F7" t="str">
+        <v>32 000 ₽</v>
+      </c>
+      <c r="G7" t="str">
         <v>34 560 ₽</v>
       </c>
-      <c r="G7" t="str">
-        <v>30 720 ₽</v>
-      </c>
       <c r="H7" t="str">
-        <v>24 320 ₽</v>
+        <v>26 880 ₽</v>
       </c>
       <c r="I7" t="str">
         <v>32 000 ₽</v>
@@ -1515,16 +1515,16 @@
         <v>32 000 ₽</v>
       </c>
       <c r="L7" t="str">
-        <v>29 440 ₽</v>
+        <v>26 880 ₽</v>
       </c>
       <c r="M7" t="str">
-        <v>28 160 ₽</v>
+        <v>25 600 ₽</v>
       </c>
       <c r="N7" t="str">
-        <v>32 000 ₽</v>
+        <v>35 840 ₽</v>
       </c>
       <c r="O7" t="str">
-        <v>32 000 ₽</v>
+        <v>34 560 ₽</v>
       </c>
       <c r="P7" t="str">
         <v>25 600 ₽</v>
@@ -1536,16 +1536,16 @@
         <v>25 600 ₽</v>
       </c>
       <c r="S7" t="str">
-        <v>29 440 ₽</v>
+        <v>26 880 ₽</v>
       </c>
       <c r="T7" t="str">
-        <v>30 720 ₽</v>
+        <v>28 160 ₽</v>
       </c>
       <c r="U7" t="str">
-        <v>27 600 ₽</v>
+        <v>30 360 ₽</v>
       </c>
       <c r="V7" t="str">
-        <v>31 740 ₽</v>
+        <v>34 500 ₽</v>
       </c>
       <c r="W7" t="str">
         <v>26 220 ₽</v>
@@ -1557,16 +1557,16 @@
         <v>30 360 ₽</v>
       </c>
       <c r="Z7" t="str">
-        <v>33 120 ₽</v>
+        <v>28 980 ₽</v>
       </c>
       <c r="AA7" t="str">
-        <v>30 360 ₽</v>
+        <v>27 600 ₽</v>
       </c>
       <c r="AB7" t="str">
-        <v>26 220 ₽</v>
+        <v>28 980 ₽</v>
       </c>
       <c r="AC7" t="str">
-        <v>28 980 ₽</v>
+        <v>31 740 ₽</v>
       </c>
       <c r="AD7" t="str">
         <v>26 220 ₽</v>
@@ -1578,16 +1578,16 @@
         <v>30 360 ₽</v>
       </c>
       <c r="AG7" t="str">
-        <v>35 880 ₽</v>
+        <v>33 120 ₽</v>
       </c>
       <c r="AH7" t="str">
-        <v>34 500 ₽</v>
+        <v>31 740 ₽</v>
       </c>
       <c r="AI7" t="str">
-        <v>25 600 ₽</v>
+        <v>28 160 ₽</v>
       </c>
       <c r="AJ7" t="str">
-        <v>29 440 ₽</v>
+        <v>32 000 ₽</v>
       </c>
       <c r="AK7" t="str">
         <v>30 720 ₽</v>
@@ -1599,16 +1599,16 @@
         <v>26 880 ₽</v>
       </c>
       <c r="AN7" t="str">
-        <v>37 120 ₽</v>
+        <v>33 280 ₽</v>
       </c>
       <c r="AO7" t="str">
+        <v>28 160 ₽</v>
+      </c>
+      <c r="AP7" t="str">
+        <v>33 280 ₽</v>
+      </c>
+      <c r="AQ7" t="str">
         <v>30 720 ₽</v>
-      </c>
-      <c r="AP7" t="str">
-        <v>29 440 ₽</v>
-      </c>
-      <c r="AQ7" t="str">
-        <v>28 160 ₽</v>
       </c>
       <c r="AR7" t="str">
         <v>33 280 ₽</v>
@@ -1620,16 +1620,16 @@
         <v>28 160 ₽</v>
       </c>
       <c r="AU7" t="str">
-        <v>34 560 ₽</v>
+        <v>32 000 ₽</v>
       </c>
       <c r="AV7" t="str">
-        <v>37 120 ₽</v>
+        <v>33 280 ₽</v>
       </c>
       <c r="AW7" t="str">
-        <v>30 720 ₽</v>
+        <v>33 280 ₽</v>
       </c>
       <c r="AX7" t="str">
-        <v>26 880 ₽</v>
+        <v>29 440 ₽</v>
       </c>
       <c r="AY7" t="str">
         <v>33 280 ₽</v>
@@ -1641,16 +1641,16 @@
         <v>32 000 ₽</v>
       </c>
       <c r="BB7" t="str">
+        <v>32 000 ₽</v>
+      </c>
+      <c r="BC7" t="str">
+        <v>28 160 ₽</v>
+      </c>
+      <c r="BD7" t="str">
+        <v>30 720 ₽</v>
+      </c>
+      <c r="BE7" t="str">
         <v>35 840 ₽</v>
-      </c>
-      <c r="BC7" t="str">
-        <v>30 720 ₽</v>
-      </c>
-      <c r="BD7" t="str">
-        <v>28 160 ₽</v>
-      </c>
-      <c r="BE7" t="str">
-        <v>33 280 ₽</v>
       </c>
       <c r="BF7" t="str">
         <v>26 880 ₽</v>
@@ -1662,16 +1662,16 @@
         <v>30 720 ₽</v>
       </c>
       <c r="BI7" t="str">
-        <v>35 840 ₽</v>
+        <v>33 280 ₽</v>
       </c>
       <c r="BJ7" t="str">
-        <v>37 120 ₽</v>
+        <v>34 560 ₽</v>
       </c>
       <c r="BK7" t="str">
-        <v>28 160 ₽</v>
+        <v>30 720 ₽</v>
       </c>
       <c r="BL7" t="str">
-        <v>33 280 ₽</v>
+        <v>34 560 ₽</v>
       </c>
       <c r="BM7" t="str">
         <v>34 560 ₽</v>
@@ -1683,16 +1683,16 @@
         <v>34 560 ₽</v>
       </c>
       <c r="BP7" t="str">
-        <v>39 680 ₽</v>
+        <v>37 120 ₽</v>
       </c>
       <c r="BQ7" t="str">
-        <v>35 840 ₽</v>
+        <v>33 280 ₽</v>
       </c>
       <c r="BR7" t="str">
-        <v>28 160 ₽</v>
+        <v>30 720 ₽</v>
       </c>
       <c r="BS7" t="str">
-        <v>29 440 ₽</v>
+        <v>32 000 ₽</v>
       </c>
     </row>
     <row r="8">
@@ -1709,16 +1709,16 @@
         <v>2209</v>
       </c>
       <c r="E8">
-        <v>2482</v>
+        <v>2265</v>
       </c>
       <c r="F8">
-        <v>2367</v>
+        <v>2159</v>
       </c>
       <c r="G8">
-        <v>2216</v>
+        <v>2430</v>
       </c>
       <c r="H8">
-        <v>2460</v>
+        <v>2697</v>
       </c>
       <c r="I8">
         <v>2412</v>
@@ -1730,16 +1730,16 @@
         <v>2421</v>
       </c>
       <c r="L8">
-        <v>2603</v>
+        <v>2371</v>
       </c>
       <c r="M8">
-        <v>2452</v>
+        <v>2233</v>
       </c>
       <c r="N8">
-        <v>2344</v>
+        <v>2575</v>
       </c>
       <c r="O8">
-        <v>2344</v>
+        <v>2575</v>
       </c>
       <c r="P8">
         <v>2299</v>
@@ -1751,16 +1751,16 @@
         <v>2202</v>
       </c>
       <c r="S8">
-        <v>2442</v>
+        <v>2221</v>
       </c>
       <c r="T8">
-        <v>2468</v>
+        <v>2245</v>
       </c>
       <c r="U8">
-        <v>2094</v>
+        <v>2303</v>
       </c>
       <c r="V8">
-        <v>2377</v>
+        <v>2614</v>
       </c>
       <c r="W8">
         <v>2083</v>
@@ -1772,16 +1772,16 @@
         <v>2448</v>
       </c>
       <c r="Z8">
-        <v>2625</v>
+        <v>2387</v>
       </c>
       <c r="AA8">
-        <v>2756</v>
+        <v>2505</v>
       </c>
       <c r="AB8">
-        <v>2494</v>
+        <v>2742</v>
       </c>
       <c r="AC8">
-        <v>2309</v>
+        <v>2539</v>
       </c>
       <c r="AD8">
         <v>2179</v>
@@ -1793,16 +1793,16 @@
         <v>2317</v>
       </c>
       <c r="AG8">
-        <v>2544</v>
+        <v>2315</v>
       </c>
       <c r="AH8">
-        <v>2761</v>
+        <v>2512</v>
       </c>
       <c r="AI8">
-        <v>2424</v>
+        <v>2663</v>
       </c>
       <c r="AJ8">
-        <v>2144</v>
+        <v>2356</v>
       </c>
       <c r="AK8">
         <v>2453</v>
@@ -1814,16 +1814,16 @@
         <v>2206</v>
       </c>
       <c r="AN8">
-        <v>2383</v>
+        <v>2171</v>
       </c>
       <c r="AO8">
-        <v>2445</v>
+        <v>2228</v>
       </c>
       <c r="AP8">
-        <v>2259</v>
+        <v>2478</v>
       </c>
       <c r="AQ8">
-        <v>2624</v>
+        <v>2877</v>
       </c>
       <c r="AR8">
         <v>2600</v>
@@ -1835,16 +1835,16 @@
         <v>2463</v>
       </c>
       <c r="AU8">
-        <v>2764</v>
+        <v>2525</v>
       </c>
       <c r="AV8">
-        <v>2641</v>
+        <v>2413</v>
       </c>
       <c r="AW8">
-        <v>2266</v>
+        <v>2479</v>
       </c>
       <c r="AX8">
-        <v>2408</v>
+        <v>2633</v>
       </c>
       <c r="AY8">
         <v>2379</v>
@@ -1856,16 +1856,16 @@
         <v>2667</v>
       </c>
       <c r="BB8">
-        <v>3015</v>
+        <v>2763</v>
       </c>
       <c r="BC8">
-        <v>2744</v>
+        <v>2515</v>
       </c>
       <c r="BD8">
-        <v>2587</v>
+        <v>2821</v>
       </c>
       <c r="BE8">
-        <v>2319</v>
+        <v>2528</v>
       </c>
       <c r="BF8">
         <v>2474</v>
@@ -1877,16 +1877,16 @@
         <v>2566</v>
       </c>
       <c r="BI8">
-        <v>2939</v>
+        <v>2702</v>
       </c>
       <c r="BJ8">
-        <v>2776</v>
+        <v>2553</v>
       </c>
       <c r="BK8">
-        <v>2396</v>
+        <v>2605</v>
       </c>
       <c r="BL8">
-        <v>2778</v>
+        <v>3018</v>
       </c>
       <c r="BM8">
         <v>2689</v>
@@ -1898,16 +1898,16 @@
         <v>2931</v>
       </c>
       <c r="BP8">
-        <v>2785</v>
+        <v>2569</v>
       </c>
       <c r="BQ8">
-        <v>2825</v>
+        <v>2606</v>
       </c>
       <c r="BR8">
-        <v>2800</v>
+        <v>3033</v>
       </c>
       <c r="BS8">
-        <v>2774</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="9">
